--- a/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,57</t>
+          <t>-1,15; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,56</t>
+          <t>-2,15; 0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,3</t>
+          <t>-0,79; 2,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 4,17</t>
+          <t>-1,59; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,6</t>
+          <t>-3,85; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,47</t>
+          <t>-2,19; 1,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,58</t>
+          <t>-0,74; 2,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -0,26</t>
+          <t>-2,33; -0,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,53</t>
+          <t>-0,89; 1,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 400,39</t>
+          <t>-68,43; 395,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 175,9</t>
+          <t>-100,0; 127,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,69; 386,77</t>
+          <t>-50,64; 422,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,32; 412,0</t>
+          <t>-51,63; 385,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 14,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,4; 140,42</t>
+          <t>-62,22; 178,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 254,22</t>
+          <t>-36,97; 228,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-93,58; -6,21</t>
+          <t>-94,56; -17,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,06; 144,36</t>
+          <t>-37,79; 147,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,16</t>
+          <t>-2,98; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,36</t>
+          <t>-2,82; 0,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,15</t>
+          <t>-1,04; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,2</t>
+          <t>-0,76; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,37</t>
+          <t>-0,71; 2,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,1</t>
+          <t>-0,09; 3,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,67</t>
+          <t>-1,64; 0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,94</t>
+          <t>-1,19; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,61</t>
+          <t>-0,12; 2,44</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 71,47</t>
+          <t>-100,0; 57,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-90,94; 140,13</t>
+          <t>-100,0; 100,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 308,3</t>
+          <t>-43,88; 323,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 1031,96</t>
+          <t>-68,46; 1023,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 1031,15</t>
+          <t>-42,76; 1146,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 106,34</t>
+          <t>-78,1; 69,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 120,95</t>
+          <t>-64,95; 145,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,3; 326,56</t>
+          <t>-7,32; 305,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,54</t>
+          <t>-0,3; 2,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,73</t>
+          <t>-1,07; 1,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,77</t>
+          <t>-1,06; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,91</t>
+          <t>-2,8; 2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 3,69</t>
+          <t>-3,28; 3,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 7,51</t>
+          <t>-0,77; 8,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,32</t>
+          <t>-0,31; 2,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,46</t>
+          <t>-1,13; 1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,22</t>
+          <t>-0,52; 3,11</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 640,27</t>
+          <t>-31,47; 675,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 492,6</t>
+          <t>-76,45; 454,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 534,64</t>
+          <t>-61,37; 558,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,82; 618,57</t>
+          <t>-84,28; 504,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,67; —</t>
+          <t>-53,83; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 422,66</t>
+          <t>-24,95; 382,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 272,84</t>
+          <t>-72,95; 229,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 419,07</t>
+          <t>-26,97; 463,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,44</t>
+          <t>-0,86; 1,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,19</t>
+          <t>-1,77; 0,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,77</t>
+          <t>-0,51; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,6</t>
+          <t>-0,42; 2,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,86</t>
+          <t>-1,51; 0,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 57,74</t>
+          <t>0,37; 52,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,45</t>
+          <t>-0,45; 1,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,18</t>
+          <t>-1,43; 0,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 36,0</t>
+          <t>0,33; 38,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 120,22</t>
+          <t>-40,59; 107,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,04; 18,61</t>
+          <t>-74,74; 27,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 136,75</t>
+          <t>-25,27; 139,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 312,09</t>
+          <t>-29,97; 255,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,59; 144,13</t>
+          <t>-71,6; 103,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,36; 8029,61</t>
+          <t>19,65; 10257,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 117,72</t>
+          <t>-24,1; 114,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 16,23</t>
+          <t>-68,26; 16,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,9; 2624,14</t>
+          <t>19,19; 2939,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,28</t>
+          <t>-3,65; 0,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,96</t>
+          <t>-3,16; 0,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,99</t>
+          <t>-1,61; 3,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,05</t>
+          <t>-0,87; 1,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,12</t>
+          <t>-1,35; 1,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,37</t>
+          <t>1,12; 4,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,93</t>
+          <t>-1,27; 0,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,66</t>
+          <t>-1,45; 0,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,2</t>
+          <t>0,69; 3,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-91,27; 43,35</t>
+          <t>-90,1; 54,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 92,65</t>
+          <t>-78,13; 99,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 260,99</t>
+          <t>-49,17; 257,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 338,15</t>
+          <t>-48,36; 315,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 191,96</t>
+          <t>-68,26; 213,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,36; 784,27</t>
+          <t>45,17; 691,16</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 88,3</t>
+          <t>-54,2; 94,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 69,87</t>
+          <t>-61,05; 77,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>18,31; 281,12</t>
+          <t>24,32; 315,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,94</t>
+          <t>-0,67; 4,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,0</t>
+          <t>-2,03; 1,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,76</t>
+          <t>-2,01; 0,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,32</t>
+          <t>-1,05; 1,36</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,1</t>
+          <t>-2,1; -0,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,36</t>
+          <t>-0,14; 2,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,2</t>
+          <t>-0,64; 1,39</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; -0,07</t>
+          <t>-1,81; -0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,7</t>
+          <t>-0,31; 1,76</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-44,15; 92,46</t>
+          <t>-41,48; 86,05</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 1,33</t>
+          <t>-80,19; 6,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 165,89</t>
+          <t>-4,91; 163,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 87,83</t>
+          <t>-29,3; 114,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,34; 0,07</t>
+          <t>-76,76; 7,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 137,24</t>
+          <t>-14,38; 121,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,74</t>
+          <t>-0,5; 0,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,07</t>
+          <t>-1,1; 0,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,45</t>
+          <t>-0,05; 1,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,14</t>
+          <t>-0,25; 1,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; -0,04</t>
+          <t>-1,16; -0,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,06; 23,77</t>
+          <t>1,13; 24,14</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,77</t>
+          <t>-0,13; 0,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; -0,2</t>
+          <t>-0,95; -0,17</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,85; 13,67</t>
+          <t>0,86; 13,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 59,55</t>
+          <t>-29,58; 58,74</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 8,07</t>
+          <t>-59,39; 2,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 108,46</t>
+          <t>-2,57; 107,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 84,01</t>
+          <t>-13,46; 85,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,82; -2,21</t>
+          <t>-58,17; -2,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,66; 1606,48</t>
+          <t>59,97; 1563,24</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 55,49</t>
+          <t>-7,86; 53,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,48; -13,9</t>
+          <t>-52,75; -11,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>49,92; 903,43</t>
+          <t>50,54; 882,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,26</t>
+          <t>-1,16; 2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,43</t>
+          <t>-2,25; 0,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,3</t>
+          <t>-0,91; 2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,0</t>
+          <t>-1,6; 3,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,48</t>
+          <t>-4,16; -0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,63</t>
+          <t>-2,15; 1,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,51</t>
+          <t>-0,85; 2,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; -0,34</t>
+          <t>-2,34; -0,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,52</t>
+          <t>-0,78; 1,58</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,45%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 395,55</t>
+          <t>-65,9; 429,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,69</t>
+          <t>-100,0; 110,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,64; 422,09</t>
+          <t>-52,82; 347,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 385,15</t>
+          <t>-56,59; 357,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 178,83</t>
+          <t>-60,12; 167,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 228,7</t>
+          <t>-41,51; 219,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-94,56; -17,8</t>
+          <t>-93,8; -9,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 147,3</t>
+          <t>-33,14; 158,36</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,14</t>
+          <t>-3,03; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,35</t>
+          <t>-2,8; 0,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,26</t>
+          <t>-0,99; 3,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,22</t>
+          <t>-0,81; 2,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,42</t>
+          <t>-0,66; 2,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,08</t>
+          <t>0,05; 3,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,51</t>
+          <t>-1,51; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,0</t>
+          <t>-1,31; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,44</t>
+          <t>-0,12; 2,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>160,6%</t>
+          <t>167,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,26</t>
+          <t>-94,29; 118,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,58</t>
+          <t>-100,0; 95,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,88; 323,99</t>
+          <t>-42,2; 355,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,46; 1023,08</t>
+          <t>-71,77; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 1146,45</t>
+          <t>-22,59; 1407,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-78,1; 69,63</t>
+          <t>-78,34; 96,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 145,72</t>
+          <t>-68,66; 137,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 305,69</t>
+          <t>-11,09; 333,6</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>2,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,74</t>
+          <t>-0,24; 2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,56</t>
+          <t>-1,13; 1,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,1</t>
+          <t>0,53; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,65</t>
+          <t>-2,76; 2,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,13</t>
+          <t>-3,09; 3,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,1</t>
+          <t>-0,91; 7,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,31</t>
+          <t>-0,31; 2,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,33</t>
+          <t>-1,16; 1,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,11</t>
+          <t>0,79; 4,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115,2%</t>
+          <t>232,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>121,84%</t>
+          <t>132,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>110,93%</t>
+          <t>199,17%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 675,72</t>
+          <t>-24,22; 831,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,45; 454,28</t>
+          <t>-81,67; 520,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 558,71</t>
+          <t>15,76; 1054,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 504,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,83; —</t>
+          <t>-65,35; 1289,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,95; 382,78</t>
+          <t>-23,32; 386,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 229,09</t>
+          <t>-69,52; 223,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 463,72</t>
+          <t>21,09; 657,1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,25</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,57</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,42</t>
+          <t>-0,95; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,23</t>
+          <t>-1,71; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,79</t>
+          <t>-0,4; 2,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,42</t>
+          <t>-0,45; 2,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,82</t>
+          <t>-1,52; 0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 52,29</t>
+          <t>-0,57; 1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,41</t>
+          <t>-0,37; 1,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,14</t>
+          <t>-1,38; 0,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 38,98</t>
+          <t>-0,1; 1,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1439,92%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>635,75%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 107,54</t>
+          <t>-43,84; 107,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 27,9</t>
+          <t>-75,87; 30,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 139,15</t>
+          <t>-21,47; 172,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 255,32</t>
+          <t>-25,11; 292,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,6; 103,94</t>
+          <t>-73,8; 106,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,65; 10257,09</t>
+          <t>-32,04; 228,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 114,84</t>
+          <t>-17,32; 117,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 16,19</t>
+          <t>-64,62; 20,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,19; 2939,48</t>
+          <t>-5,18; 148,17</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,22</t>
+          <t>-3,46; 0,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,92</t>
+          <t>-3,1; 0,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,01</t>
+          <t>-2,17; 2,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,98</t>
+          <t>-0,92; 1,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,15</t>
+          <t>-1,44; 1,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,33</t>
+          <t>1,84; 4,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,99</t>
+          <t>-1,26; 0,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,76</t>
+          <t>-1,54; 0,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,31</t>
+          <t>0,85; 3,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>218,56%</t>
+          <t>259,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118,19%</t>
+          <t>126,98%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,1; 54,31</t>
+          <t>-90,35; 35,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 99,05</t>
+          <t>-82,74; 69,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 257,49</t>
+          <t>-59,28; 189,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,36; 315,77</t>
+          <t>-45,15; 332,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 213,06</t>
+          <t>-68,91; 180,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,17; 691,16</t>
+          <t>73,71; 792,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 94,66</t>
+          <t>-57,55; 83,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 77,68</t>
+          <t>-63,47; 75,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24,32; 315,45</t>
+          <t>31,84; 309,67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>0,45</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>1,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,24</t>
+          <t>-0,68; 4,17</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,01</t>
+          <t>-1,81; 1,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,86</t>
+          <t>-1,05; 3,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,36</t>
+          <t>-1,1; 1,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,04</t>
+          <t>-2,21; -0,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,35</t>
+          <t>0,02; 2,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,39</t>
+          <t>-0,71; 1,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; -0,0</t>
+          <t>-1,76; -0,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,76</t>
+          <t>0,09; 2,45</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-31,26%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>68,34%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 86,05</t>
+          <t>-43,57; 94,7</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,19; 6,48</t>
+          <t>-80,68; -3,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 163,78</t>
+          <t>-1,74; 195,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 114,4</t>
+          <t>-32,26; 110,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-76,76; 7,17</t>
+          <t>-76,75; 3,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 121,79</t>
+          <t>1,23; 174,36</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,77</t>
+          <t>-0,49; 0,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,01</t>
+          <t>-1,16; 0,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,37</t>
+          <t>0,24; 1,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,15</t>
+          <t>-0,19; 1,16</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; -0,04</t>
+          <t>-1,13; -0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,13; 24,14</t>
+          <t>0,89; 2,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 0,75</t>
+          <t>-0,14; 0,77</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; -0,17</t>
+          <t>-0,98; -0,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,93</t>
+          <t>0,74; 1,73</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>413,66%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>240,54%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 58,74</t>
+          <t>-27,12; 61,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 2,24</t>
+          <t>-59,24; 9,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 107,2</t>
+          <t>10,88; 135,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 85,44</t>
+          <t>-11,42; 84,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-58,17; -2,84</t>
+          <t>-57,06; 1,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>59,97; 1563,24</t>
+          <t>42,83; 160,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 53,76</t>
+          <t>-7,95; 56,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -11,55</t>
+          <t>-52,5; -10,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,54; 882,52</t>
+          <t>38,3; 124,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
